--- a/public/files/import/template_products_update_price (1).xlsx
+++ b/public/files/import/template_products_update_price (1).xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="17">
   <si>
     <t>Mã sản phẩm</t>
   </si>
@@ -38,64 +38,34 @@
     <t>Giá: Khách lẻ</t>
   </si>
   <si>
-    <t>sp04</t>
+    <t>SP001</t>
+  </si>
+  <si>
+    <t>Sản phẩm 01</t>
+  </si>
+  <si>
+    <t>SP002</t>
+  </si>
+  <si>
+    <t>Sản phẩm 02</t>
+  </si>
+  <si>
+    <t>SP003</t>
+  </si>
+  <si>
+    <t>Sản phẩm 03</t>
+  </si>
+  <si>
+    <t>SP004</t>
   </si>
   <si>
     <t>Sản phẩm 04</t>
   </si>
   <si>
-    <t>sp02</t>
-  </si>
-  <si>
-    <t>sản phẩm 2</t>
-  </si>
-  <si>
-    <t>SP03</t>
-  </si>
-  <si>
-    <t>Thảm da cao cấp</t>
-  </si>
-  <si>
-    <t>SP01</t>
-  </si>
-  <si>
-    <t>SP10</t>
-  </si>
-  <si>
-    <t>Thảm sàn nhựa đúc VF3</t>
-  </si>
-  <si>
-    <t>SP11</t>
-  </si>
-  <si>
-    <t>Thảm sàn nhựa đúc VF4</t>
-  </si>
-  <si>
-    <t>SP05</t>
-  </si>
-  <si>
-    <t>Thảm sàn nhựa đúc VF6</t>
-  </si>
-  <si>
-    <t>SP06</t>
-  </si>
-  <si>
-    <t>SP07</t>
-  </si>
-  <si>
-    <t>Thảm sàn nhựa đúc VF7</t>
-  </si>
-  <si>
-    <t>SP08</t>
-  </si>
-  <si>
-    <t>Thảm sàn nhựa đúc VF8</t>
-  </si>
-  <si>
-    <t>SP09</t>
-  </si>
-  <si>
-    <t>Thảm sàn nhựa đúc VF9</t>
+    <t>SP005</t>
+  </si>
+  <si>
+    <t>Sản phẩm 05</t>
   </si>
 </sst>
 </file>
@@ -446,11 +416,11 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="13.996582" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="25.85083" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="15.281982" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="10.568848" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="21.137695" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="21.137695" bestFit="true" customWidth="true" style="0"/>
@@ -489,19 +459,19 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>250000</v>
+        <v>750000</v>
       </c>
       <c r="D2">
-        <v>200000</v>
+        <v>23000</v>
       </c>
       <c r="E2">
-        <v>300000</v>
+        <v>900000</v>
       </c>
       <c r="F2">
-        <v>400000</v>
+        <v>1050000</v>
       </c>
       <c r="G2">
-        <v>500000</v>
+        <v>1125000</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -512,19 +482,19 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>150000</v>
+        <v>800000</v>
       </c>
       <c r="D3">
-        <v>150000</v>
+        <v>23000</v>
       </c>
       <c r="E3">
-        <v>180000</v>
+        <v>960000</v>
       </c>
       <c r="F3">
-        <v>200000</v>
+        <v>1120000</v>
       </c>
       <c r="G3">
-        <v>250000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -535,19 +505,19 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>150000</v>
+        <v>850000</v>
       </c>
       <c r="D4">
-        <v>15000</v>
+        <v>23000</v>
       </c>
       <c r="E4">
-        <v>20000</v>
+        <v>1020000</v>
       </c>
       <c r="F4">
-        <v>25000</v>
+        <v>1190000</v>
       </c>
       <c r="G4">
-        <v>30000</v>
+        <v>1275000</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -555,183 +525,45 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>150000</v>
+        <v>900000</v>
       </c>
       <c r="D5">
-        <v>500</v>
+        <v>23000</v>
       </c>
       <c r="E5">
-        <v>1000</v>
+        <v>1080000</v>
       </c>
       <c r="F5">
-        <v>2000</v>
+        <v>1260000</v>
       </c>
       <c r="G5">
-        <v>3000</v>
+        <v>1350000</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6">
-        <v>890000</v>
+        <v>950000</v>
       </c>
       <c r="D6">
-        <v>1500000</v>
+        <v>23000</v>
       </c>
       <c r="E6">
-        <v>1800000</v>
+        <v>1140000</v>
       </c>
       <c r="F6">
-        <v>2000000</v>
+        <v>1330000</v>
       </c>
       <c r="G6">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>890000</v>
-      </c>
-      <c r="D7">
-        <v>1500000</v>
-      </c>
-      <c r="E7">
-        <v>1800000</v>
-      </c>
-      <c r="F7">
-        <v>2000000</v>
-      </c>
-      <c r="G7">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8">
-        <v>890000</v>
-      </c>
-      <c r="D8">
-        <v>1500000</v>
-      </c>
-      <c r="E8">
-        <v>1800000</v>
-      </c>
-      <c r="F8">
-        <v>2000000</v>
-      </c>
-      <c r="G8">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9">
-        <v>890000</v>
-      </c>
-      <c r="D9">
-        <v>1500000</v>
-      </c>
-      <c r="E9">
-        <v>1800000</v>
-      </c>
-      <c r="F9">
-        <v>2000000</v>
-      </c>
-      <c r="G9">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10">
-        <v>680000</v>
-      </c>
-      <c r="D10">
-        <v>1500000</v>
-      </c>
-      <c r="E10">
-        <v>1800000</v>
-      </c>
-      <c r="F10">
-        <v>2000000</v>
-      </c>
-      <c r="G10">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11">
-        <v>890000</v>
-      </c>
-      <c r="D11">
-        <v>140000</v>
-      </c>
-      <c r="E11">
-        <v>1800000</v>
-      </c>
-      <c r="F11">
-        <v>2000000</v>
-      </c>
-      <c r="G11">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12">
-        <v>890000</v>
-      </c>
-      <c r="D12">
-        <v>1500000</v>
-      </c>
-      <c r="E12">
-        <v>180000</v>
-      </c>
-      <c r="F12">
-        <v>2000000</v>
-      </c>
-      <c r="G12">
-        <v>2500000</v>
+        <v>1425000</v>
       </c>
     </row>
   </sheetData>
